--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
   <si>
     <t>Código Produto</t>
   </si>
@@ -91,6 +91,15 @@
     <t>HONMMT-01</t>
   </si>
   <si>
+    <t>YSI103740Y</t>
+  </si>
+  <si>
+    <t>YSI109813Y</t>
+  </si>
+  <si>
+    <t>YSI1FD560Y</t>
+  </si>
+  <si>
     <t>SENSOR ELETROQUIMICO DE H2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
   </si>
   <si>
@@ -106,6 +115,15 @@
     <t>ANALISADOR FIXO PARA 4 GASES - MODELO MIDAS M</t>
   </si>
   <si>
+    <t>SENSOR YSI IDS COMBINADO DE PH E TEMPERATURA - CABO DE 1,5 METROS</t>
+  </si>
+  <si>
+    <t>SUPORTE PARA SENSORES IDS PARA INSTRUMENTOS YSI MULTILAB</t>
+  </si>
+  <si>
+    <t>ANALISADOR DE BANCADA YSI MULTILAB IDS (DUPLO CANAL)</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -118,6 +136,9 @@
     <t>133701</t>
   </si>
   <si>
+    <t>999999</t>
+  </si>
+  <si>
     <t>FATURADO</t>
   </si>
   <si>
@@ -127,21 +148,39 @@
     <t>ANDREY.ANDRADE</t>
   </si>
   <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
     <t>LEONARDO DO CARMO</t>
   </si>
   <si>
+    <t xml:space="preserve">KELLY AMARAL BISPO                      </t>
+  </si>
+  <si>
     <t>DEPART. DETECÇÃO FIXA GASES</t>
   </si>
   <si>
+    <t>HIDROLOGIA</t>
+  </si>
+  <si>
     <t>22853</t>
   </si>
   <si>
+    <t>8648</t>
+  </si>
+  <si>
     <t>AMYRIS FERMENTACAO DE PERFORMANCE LTDA</t>
   </si>
   <si>
+    <t>BRK AMBIENTAL - RIO CLARO S.A.</t>
+  </si>
+  <si>
     <t>BARRA BONITA</t>
   </si>
   <si>
+    <t>RIO CLARO</t>
+  </si>
+  <si>
     <t>SP</t>
   </si>
   <si>
@@ -160,10 +199,22 @@
     <t>Midas</t>
   </si>
   <si>
+    <t>MULTILAB</t>
+  </si>
+  <si>
     <t>Detector Fixo</t>
   </si>
   <si>
+    <t>Sonda Portátil</t>
+  </si>
+  <si>
+    <t>Sonda Serie MultiLab</t>
+  </si>
+  <si>
     <t>SSO</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
   </si>
 </sst>
 </file>
@@ -525,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -595,61 +646,61 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2">
         <v>45851</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="R2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -657,61 +708,61 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2">
         <v>45851</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="R3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -719,61 +770,61 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2">
         <v>45851</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="S4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="T4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -781,61 +832,61 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2">
         <v>45851</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="S5" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="T5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -843,61 +894,238 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2">
         <v>45851</v>
       </c>
       <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O6" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>57</v>
+      </c>
+      <c r="R6" t="s">
+        <v>60</v>
+      </c>
+      <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45840</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" t="s">
+        <v>52</v>
+      </c>
+      <c r="O7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>56</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>63</v>
+      </c>
+      <c r="T7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="2">
+        <v>45841</v>
+      </c>
+      <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" t="s">
+        <v>52</v>
+      </c>
+      <c r="O8" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>56</v>
+      </c>
+      <c r="R8" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" t="s">
+        <v>63</v>
+      </c>
+      <c r="T8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="I6" t="s">
+      <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="D9" t="s">
         <v>38</v>
       </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="E9" t="s">
         <v>40</v>
       </c>
-      <c r="O6" t="s">
+      <c r="F9" t="s">
         <v>41</v>
       </c>
-      <c r="P6" t="s">
+      <c r="G9" s="2">
+        <v>45842</v>
+      </c>
+      <c r="H9" t="s">
         <v>42</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="I9" t="s">
         <v>44</v>
       </c>
-      <c r="R6" t="s">
-        <v>47</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" t="s">
         <v>48</v>
       </c>
-      <c r="T6" t="s">
-        <v>49</v>
+      <c r="M9" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R9" t="s">
+        <v>61</v>
+      </c>
+      <c r="S9" t="s">
+        <v>64</v>
+      </c>
+      <c r="T9" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="50">
   <si>
     <t>Código Produto</t>
   </si>
@@ -91,15 +91,6 @@
     <t>HONMMT-01</t>
   </si>
   <si>
-    <t>YSI103740Y</t>
-  </si>
-  <si>
-    <t>YSI109813Y</t>
-  </si>
-  <si>
-    <t>YSI1FD560Y</t>
-  </si>
-  <si>
     <t>SENSOR ELETROQUIMICO DE H2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
   </si>
   <si>
@@ -115,15 +106,6 @@
     <t>ANALISADOR FIXO PARA 4 GASES - MODELO MIDAS M</t>
   </si>
   <si>
-    <t>SENSOR YSI IDS COMBINADO DE PH E TEMPERATURA - CABO DE 1,5 METROS</t>
-  </si>
-  <si>
-    <t>SUPORTE PARA SENSORES IDS PARA INSTRUMENTOS YSI MULTILAB</t>
-  </si>
-  <si>
-    <t>ANALISADOR DE BANCADA YSI MULTILAB IDS (DUPLO CANAL)</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -136,9 +118,6 @@
     <t>133701</t>
   </si>
   <si>
-    <t>999999</t>
-  </si>
-  <si>
     <t>FATURADO</t>
   </si>
   <si>
@@ -148,39 +127,21 @@
     <t>ANDREY.ANDRADE</t>
   </si>
   <si>
-    <t>SAMANTA</t>
-  </si>
-  <si>
     <t>LEONARDO DO CARMO</t>
   </si>
   <si>
-    <t xml:space="preserve">KELLY AMARAL BISPO                      </t>
-  </si>
-  <si>
     <t>DEPART. DETECÇÃO FIXA GASES</t>
   </si>
   <si>
-    <t>HIDROLOGIA</t>
-  </si>
-  <si>
     <t>22853</t>
   </si>
   <si>
-    <t>8648</t>
-  </si>
-  <si>
     <t>AMYRIS FERMENTACAO DE PERFORMANCE LTDA</t>
   </si>
   <si>
-    <t>BRK AMBIENTAL - RIO CLARO S.A.</t>
-  </si>
-  <si>
     <t>BARRA BONITA</t>
   </si>
   <si>
-    <t>RIO CLARO</t>
-  </si>
-  <si>
     <t>SP</t>
   </si>
   <si>
@@ -199,22 +160,10 @@
     <t>Midas</t>
   </si>
   <si>
-    <t>MULTILAB</t>
-  </si>
-  <si>
     <t>Detector Fixo</t>
   </si>
   <si>
-    <t>Sonda Portátil</t>
-  </si>
-  <si>
-    <t>Sonda Serie MultiLab</t>
-  </si>
-  <si>
     <t>SSO</t>
-  </si>
-  <si>
-    <t>Hidrologia</t>
   </si>
 </sst>
 </file>
@@ -576,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -646,61 +595,61 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s">
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="E2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" t="s">
+      <c r="N2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="2">
-        <v>45851</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="P2" t="s">
         <v>42</v>
       </c>
-      <c r="I2" t="s">
+      <c r="Q2" t="s">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="R2" t="s">
         <v>45</v>
       </c>
-      <c r="K2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="S2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" t="s">
         <v>49</v>
-      </c>
-      <c r="N2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O2" t="s">
-        <v>53</v>
-      </c>
-      <c r="P2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>56</v>
-      </c>
-      <c r="R2" t="s">
-        <v>58</v>
-      </c>
-      <c r="S2" t="s">
-        <v>62</v>
-      </c>
-      <c r="T2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -708,61 +657,61 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
         <v>38</v>
       </c>
-      <c r="E3" t="s">
+      <c r="M3" t="s">
         <v>39</v>
       </c>
-      <c r="F3" t="s">
+      <c r="N3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="2">
-        <v>45851</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="P3" t="s">
         <v>42</v>
       </c>
-      <c r="I3" t="s">
+      <c r="Q3" t="s">
         <v>43</v>
       </c>
-      <c r="J3" t="s">
+      <c r="R3" t="s">
         <v>45</v>
       </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="S3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" t="s">
         <v>49</v>
-      </c>
-      <c r="N3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O3" t="s">
-        <v>53</v>
-      </c>
-      <c r="P3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>56</v>
-      </c>
-      <c r="R3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S3" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -770,61 +719,61 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" t="s">
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" t="s">
+      <c r="M4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" t="s">
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="2">
-        <v>45851</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="P4" t="s">
         <v>42</v>
       </c>
-      <c r="I4" t="s">
+      <c r="Q4" t="s">
         <v>43</v>
       </c>
-      <c r="J4" t="s">
+      <c r="R4" t="s">
         <v>45</v>
       </c>
-      <c r="K4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="S4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" t="s">
         <v>49</v>
-      </c>
-      <c r="N4" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P4" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>56</v>
-      </c>
-      <c r="R4" t="s">
-        <v>58</v>
-      </c>
-      <c r="S4" t="s">
-        <v>62</v>
-      </c>
-      <c r="T4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -832,61 +781,61 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
         <v>38</v>
       </c>
-      <c r="E5" t="s">
+      <c r="M5" t="s">
         <v>39</v>
       </c>
-      <c r="F5" t="s">
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="2">
-        <v>45851</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="P5" t="s">
         <v>42</v>
       </c>
-      <c r="I5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="Q5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" t="s">
         <v>49</v>
-      </c>
-      <c r="N5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" t="s">
-        <v>53</v>
-      </c>
-      <c r="P5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R5" t="s">
-        <v>59</v>
-      </c>
-      <c r="S5" t="s">
-        <v>62</v>
-      </c>
-      <c r="T5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -894,238 +843,61 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
         <v>36</v>
       </c>
-      <c r="D6" t="s">
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" t="s">
+      <c r="M6" t="s">
         <v>39</v>
       </c>
-      <c r="F6" t="s">
+      <c r="N6" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="2">
-        <v>45851</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="P6" t="s">
         <v>42</v>
       </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="Q6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6" t="s">
         <v>47</v>
       </c>
-      <c r="M6" t="s">
+      <c r="S6" t="s">
+        <v>48</v>
+      </c>
+      <c r="T6" t="s">
         <v>49</v>
-      </c>
-      <c r="N6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>57</v>
-      </c>
-      <c r="R6" t="s">
-        <v>60</v>
-      </c>
-      <c r="S6" t="s">
-        <v>62</v>
-      </c>
-      <c r="T6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="2">
-        <v>45840</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" t="s">
-        <v>52</v>
-      </c>
-      <c r="O7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>56</v>
-      </c>
-      <c r="R7" t="s">
-        <v>58</v>
-      </c>
-      <c r="S7" t="s">
-        <v>63</v>
-      </c>
-      <c r="T7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="2">
-        <v>45841</v>
-      </c>
-      <c r="H8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" t="s">
-        <v>52</v>
-      </c>
-      <c r="O8" t="s">
-        <v>54</v>
-      </c>
-      <c r="P8" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>56</v>
-      </c>
-      <c r="R8" t="s">
-        <v>59</v>
-      </c>
-      <c r="S8" t="s">
-        <v>63</v>
-      </c>
-      <c r="T8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="2">
-        <v>45842</v>
-      </c>
-      <c r="H9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" t="s">
-        <v>52</v>
-      </c>
-      <c r="O9" t="s">
-        <v>54</v>
-      </c>
-      <c r="P9" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R9" t="s">
-        <v>61</v>
-      </c>
-      <c r="S9" t="s">
-        <v>64</v>
-      </c>
-      <c r="T9" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Código Produto</t>
   </si>
@@ -76,46 +76,16 @@
     <t>Negócio</t>
   </si>
   <si>
-    <t>HONMMS-G2</t>
-  </si>
-  <si>
-    <t>HONMMS-TR</t>
-  </si>
-  <si>
-    <t>HONMMS-D2</t>
-  </si>
-  <si>
-    <t>ANGLTA2051WJ24V-IND</t>
-  </si>
-  <si>
-    <t>HONMMT-01</t>
-  </si>
-  <si>
-    <t>SENSOR ELETROQUIMICO DE H2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SENSOR IR DE CO2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SENSOR DE OXIGÊNIO PARA USO NO ANALISADOR DE GASES MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SIRENE P/ SISTEMA DE DETECÇÃO FIXA SAV-C 24V</t>
-  </si>
-  <si>
-    <t>ANALISADOR FIXO PARA 4 GASES - MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PVEN - PEDIDO DE VENDA</t>
-  </si>
-  <si>
-    <t>133701</t>
+    <t>QED-AP4-RET</t>
+  </si>
+  <si>
+    <t>Teste Retenção (Neimar)</t>
+  </si>
+  <si>
+    <t>PVEN</t>
+  </si>
+  <si>
+    <t>999999</t>
   </si>
   <si>
     <t>FATURADO</t>
@@ -124,46 +94,22 @@
     <t>100</t>
   </si>
   <si>
-    <t>ANDREY.ANDRADE</t>
-  </si>
-  <si>
-    <t>LEONARDO DO CARMO</t>
-  </si>
-  <si>
-    <t>DEPART. DETECÇÃO FIXA GASES</t>
-  </si>
-  <si>
-    <t>22853</t>
-  </si>
-  <si>
-    <t>AMYRIS FERMENTACAO DE PERFORMANCE LTDA</t>
-  </si>
-  <si>
-    <t>BARRA BONITA</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>Reposição</t>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>Cliente Teste1</t>
   </si>
   <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>Sensor</t>
-  </si>
-  <si>
-    <t>Acessório</t>
-  </si>
-  <si>
-    <t>Midas</t>
-  </si>
-  <si>
-    <t>Detector Fixo</t>
-  </si>
-  <si>
-    <t>SSO</t>
+    <t>Auto Pump</t>
+  </si>
+  <si>
+    <t>Elevador de Liquidos Fixo</t>
+  </si>
+  <si>
+    <t>Remediação</t>
   </si>
 </sst>
 </file>
@@ -525,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -595,309 +541,40 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45918</v>
+      </c>
+      <c r="H2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45882</v>
-      </c>
-      <c r="H2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" t="s">
-        <v>48</v>
-      </c>
       <c r="T2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45882</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="2">
-        <v>45882</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
         <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="2">
-        <v>45882</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>44</v>
-      </c>
-      <c r="R5" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="2">
-        <v>45882</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>44</v>
-      </c>
-      <c r="R6" t="s">
-        <v>47</v>
-      </c>
-      <c r="S6" t="s">
-        <v>48</v>
-      </c>
-      <c r="T6" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="50">
   <si>
     <t>Código Produto</t>
   </si>
@@ -76,16 +76,46 @@
     <t>Negócio</t>
   </si>
   <si>
-    <t>QED-AP4-RET</t>
-  </si>
-  <si>
-    <t>Teste Retenção (Neimar)</t>
-  </si>
-  <si>
-    <t>PVEN</t>
-  </si>
-  <si>
-    <t>999999</t>
+    <t>HONMMS-G2</t>
+  </si>
+  <si>
+    <t>HONMMS-TR</t>
+  </si>
+  <si>
+    <t>HONMMS-D2</t>
+  </si>
+  <si>
+    <t>ANGLTA2051WJ24V-IND</t>
+  </si>
+  <si>
+    <t>HONMMT-01</t>
+  </si>
+  <si>
+    <t>SENSOR ELETROQUIMICO DE H2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
+  </si>
+  <si>
+    <t>SENSOR IR DE CO2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
+  </si>
+  <si>
+    <t>SENSOR DE OXIGÊNIO PARA USO NO ANALISADOR DE GASES MODELO MIDAS M</t>
+  </si>
+  <si>
+    <t>SIRENE P/ SISTEMA DE DETECÇÃO FIXA SAV-C 24V</t>
+  </si>
+  <si>
+    <t>ANALISADOR FIXO PARA 4 GASES - MODELO MIDAS M</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PVEN - PEDIDO DE VENDA</t>
+  </si>
+  <si>
+    <t>133701</t>
   </si>
   <si>
     <t>FATURADO</t>
@@ -94,22 +124,46 @@
     <t>100</t>
   </si>
   <si>
-    <t>DENER.MARTINS</t>
-  </si>
-  <si>
-    <t>Cliente Teste1</t>
+    <t>ANDREY.ANDRADE</t>
+  </si>
+  <si>
+    <t>LEONARDO DO CARMO</t>
+  </si>
+  <si>
+    <t>DEPART. DETECÇÃO FIXA GASES</t>
+  </si>
+  <si>
+    <t>22853</t>
+  </si>
+  <si>
+    <t>AMYRIS FERMENTACAO DE PERFORMANCE LTDA</t>
+  </si>
+  <si>
+    <t>BARRA BONITA</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Reposição</t>
   </si>
   <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>Auto Pump</t>
-  </si>
-  <si>
-    <t>Elevador de Liquidos Fixo</t>
-  </si>
-  <si>
-    <t>Remediação</t>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Acessório</t>
+  </si>
+  <si>
+    <t>Midas</t>
+  </si>
+  <si>
+    <t>Detector Fixo</t>
+  </si>
+  <si>
+    <t>SSO</t>
   </si>
 </sst>
 </file>
@@ -471,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -541,40 +595,309 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="2">
-        <v>45918</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="S2" t="s">
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="T2" t="s">
-        <v>31</v>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6" t="s">
+        <v>47</v>
+      </c>
+      <c r="S6" t="s">
+        <v>48</v>
+      </c>
+      <c r="T6" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -610,7 +610,7 @@
         <v>34</v>
       </c>
       <c r="G2" s="2">
-        <v>45882</v>
+        <v>45913</v>
       </c>
       <c r="H2" t="s">
         <v>35</v>
@@ -672,7 +672,7 @@
         <v>34</v>
       </c>
       <c r="G3" s="2">
-        <v>45882</v>
+        <v>45913</v>
       </c>
       <c r="H3" t="s">
         <v>35</v>
@@ -734,7 +734,7 @@
         <v>34</v>
       </c>
       <c r="G4" s="2">
-        <v>45882</v>
+        <v>45913</v>
       </c>
       <c r="H4" t="s">
         <v>35</v>
@@ -796,7 +796,7 @@
         <v>34</v>
       </c>
       <c r="G5" s="2">
-        <v>45882</v>
+        <v>45913</v>
       </c>
       <c r="H5" t="s">
         <v>35</v>
@@ -858,7 +858,7 @@
         <v>34</v>
       </c>
       <c r="G6" s="2">
-        <v>45882</v>
+        <v>45913</v>
       </c>
       <c r="H6" t="s">
         <v>35</v>

--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>Código Produto</t>
   </si>
@@ -76,46 +76,16 @@
     <t>Negócio</t>
   </si>
   <si>
-    <t>HONMMS-G2</t>
-  </si>
-  <si>
-    <t>HONMMS-TR</t>
-  </si>
-  <si>
-    <t>HONMMS-D2</t>
-  </si>
-  <si>
-    <t>ANGLTA2051WJ24V-IND</t>
-  </si>
-  <si>
-    <t>HONMMT-01</t>
-  </si>
-  <si>
-    <t>SENSOR ELETROQUIMICO DE H2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SENSOR IR DE CO2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SENSOR DE OXIGÊNIO PARA USO NO ANALISADOR DE GASES MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SIRENE P/ SISTEMA DE DETECÇÃO FIXA SAV-C 24V</t>
-  </si>
-  <si>
-    <t>ANALISADOR FIXO PARA 4 GASES - MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PVEN - PEDIDO DE VENDA</t>
-  </si>
-  <si>
-    <t>133701</t>
+    <t>QED-AP4-RET</t>
+  </si>
+  <si>
+    <t>Teste Retenção (Neimar)</t>
+  </si>
+  <si>
+    <t>PVEN</t>
+  </si>
+  <si>
+    <t>999999</t>
   </si>
   <si>
     <t>FATURADO</t>
@@ -124,46 +94,22 @@
     <t>100</t>
   </si>
   <si>
-    <t>ANDREY.ANDRADE</t>
-  </si>
-  <si>
-    <t>LEONARDO DO CARMO</t>
-  </si>
-  <si>
-    <t>DEPART. DETECÇÃO FIXA GASES</t>
-  </si>
-  <si>
-    <t>22853</t>
-  </si>
-  <si>
-    <t>AMYRIS FERMENTACAO DE PERFORMANCE LTDA</t>
-  </si>
-  <si>
-    <t>BARRA BONITA</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>Reposição</t>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>Cliente Teste2</t>
   </si>
   <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>Sensor</t>
-  </si>
-  <si>
-    <t>Acessório</t>
-  </si>
-  <si>
-    <t>Midas</t>
-  </si>
-  <si>
-    <t>Detector Fixo</t>
-  </si>
-  <si>
-    <t>SSO</t>
+    <t>Auto Pump</t>
+  </si>
+  <si>
+    <t>Elevador de Liquidos Fixo</t>
+  </si>
+  <si>
+    <t>Remediação</t>
   </si>
 </sst>
 </file>
@@ -525,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -595,309 +541,81 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45905</v>
+      </c>
+      <c r="H2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45913</v>
-      </c>
-      <c r="H2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" t="s">
-        <v>48</v>
-      </c>
       <c r="T2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45905</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" t="s">
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45913</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" t="s">
-        <v>48</v>
-      </c>
       <c r="T3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="2">
-        <v>45913</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
         <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="2">
-        <v>45913</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>44</v>
-      </c>
-      <c r="R5" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="2">
-        <v>45913</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>44</v>
-      </c>
-      <c r="R6" t="s">
-        <v>47</v>
-      </c>
-      <c r="S6" t="s">
-        <v>48</v>
-      </c>
-      <c r="T6" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -1,144 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
-  <si>
-    <t>Código Produto</t>
-  </si>
-  <si>
-    <t>Descrição Produto</t>
-  </si>
-  <si>
-    <t>Qtde Atendida</t>
-  </si>
-  <si>
-    <t>Operação</t>
-  </si>
-  <si>
-    <t>Processo</t>
-  </si>
-  <si>
-    <t>Status Processo</t>
-  </si>
-  <si>
-    <t>Dt Emissão</t>
-  </si>
-  <si>
-    <t>Valor Realizado</t>
-  </si>
-  <si>
-    <t>Consultor Interno</t>
-  </si>
-  <si>
-    <t>Representante-pedido</t>
-  </si>
-  <si>
-    <t>Gerente Comercial-Pedido</t>
-  </si>
-  <si>
-    <t>Aplicação Mat./Serv.</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Nome Cliente</t>
-  </si>
-  <si>
-    <t>Cidade</t>
-  </si>
-  <si>
-    <t>UF</t>
-  </si>
-  <si>
-    <t>Tipo de Mercadoria</t>
-  </si>
-  <si>
-    <t>Subgrupo</t>
-  </si>
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Negócio</t>
-  </si>
-  <si>
-    <t>QED-AP4-RET</t>
-  </si>
-  <si>
-    <t>Teste Retenção (Neimar)</t>
-  </si>
-  <si>
-    <t>PVEN</t>
-  </si>
-  <si>
-    <t>999999</t>
-  </si>
-  <si>
-    <t>FATURADO</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>DENER.MARTINS</t>
-  </si>
-  <si>
-    <t>Cliente Teste2</t>
-  </si>
-  <si>
-    <t>Produto</t>
-  </si>
-  <si>
-    <t>Auto Pump</t>
-  </si>
-  <si>
-    <t>Elevador de Liquidos Fixo</t>
-  </si>
-  <si>
-    <t>Remediação</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -153,36 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -470,155 +424,189 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código Produto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Descrição Produto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Qtde Atendida</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Operação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status Processo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Dt Emissão</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Realizado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Consultor Interno</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Representante-pedido</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Gerente Comercial-Pedido</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Aplicação Mat./Serv.</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Nome Cliente</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Cidade</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Mercadoria</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Subgrupo</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Negócio</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45905</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45905</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3" t="s">
-        <v>29</v>
-      </c>
-      <c r="S3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" t="s">
-        <v>31</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QED-AP4-RET</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Teste Retenção (Neimar)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PVEN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>9999991</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DENER.MARTINS</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Cliente Teste2</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Auto Pump</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Elevador de Liquidos Fixo</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Remediação</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -1,40 +1,147 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>Código Produto</t>
+  </si>
+  <si>
+    <t>Descrição Produto</t>
+  </si>
+  <si>
+    <t>Qtde Atendida</t>
+  </si>
+  <si>
+    <t>Operação</t>
+  </si>
+  <si>
+    <t>Processo</t>
+  </si>
+  <si>
+    <t>Status Processo</t>
+  </si>
+  <si>
+    <t>Dt Emissão</t>
+  </si>
+  <si>
+    <t>Valor Realizado</t>
+  </si>
+  <si>
+    <t>Consultor Interno</t>
+  </si>
+  <si>
+    <t>Representante-pedido</t>
+  </si>
+  <si>
+    <t>Gerente Comercial-Pedido</t>
+  </si>
+  <si>
+    <t>Aplicação Mat./Serv.</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Nome Cliente</t>
+  </si>
+  <si>
+    <t>Cidade</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>Tipo de Mercadoria</t>
+  </si>
+  <si>
+    <t>Subgrupo</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Negócio</t>
+  </si>
+  <si>
+    <t>HON-MCXL-BASE</t>
+  </si>
+  <si>
+    <t>Base Teste FC</t>
+  </si>
+  <si>
+    <t>PVEN</t>
+  </si>
+  <si>
+    <t>FC-Base3</t>
+  </si>
+  <si>
+    <t>FATURADO</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Andrey Andrade</t>
+  </si>
+  <si>
+    <t>André Camargo</t>
+  </si>
+  <si>
+    <t>Cliente Teste</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>MicroClip</t>
+  </si>
+  <si>
+    <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>SSO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +156,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -424,189 +473,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Código Produto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Descrição Produto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Qtde Atendida</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Operação</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Processo</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Status Processo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Dt Emissão</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Realizado</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Consultor Interno</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Representante-pedido</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Gerente Comercial-Pedido</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Aplicação Mat./Serv.</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Nome Cliente</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Cidade</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>UF</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Mercadoria</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Subgrupo</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Negócio</t>
-        </is>
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QED-AP4-RET</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Teste Retenção (Neimar)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PVEN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>9999991</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>FATURADO</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>DENER.MARTINS</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Cliente Teste2</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Auto Pump</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Elevador de Liquidos Fixo</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Remediação</t>
-        </is>
+    <row r="2" spans="1:20">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45915</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>Código Produto</t>
   </si>
@@ -85,7 +85,10 @@
     <t>PVEN</t>
   </si>
   <si>
-    <t>FC-Base3</t>
+    <t>999999</t>
+  </si>
+  <si>
+    <t>999998</t>
   </si>
   <si>
     <t>FATURADO</t>
@@ -100,7 +103,7 @@
     <t>André Camargo</t>
   </si>
   <si>
-    <t>Cliente Teste</t>
+    <t>005309</t>
   </si>
   <si>
     <t>Produto</t>
@@ -474,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -553,34 +556,78 @@
         <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="2">
         <v>45915</v>
       </c>
       <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G3" s="2">
+        <v>45915</v>
+      </c>
+      <c r="H3" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="J3" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="M3" t="s">
         <v>29</v>
       </c>
-      <c r="R2" t="s">
+      <c r="Q3" t="s">
         <v>30</v>
       </c>
-      <c r="S2" t="s">
+      <c r="R3" t="s">
         <v>31</v>
       </c>
-      <c r="T2" t="s">
+      <c r="S3" t="s">
         <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -1,150 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
-  <si>
-    <t>Código Produto</t>
-  </si>
-  <si>
-    <t>Descrição Produto</t>
-  </si>
-  <si>
-    <t>Qtde Atendida</t>
-  </si>
-  <si>
-    <t>Operação</t>
-  </si>
-  <si>
-    <t>Processo</t>
-  </si>
-  <si>
-    <t>Status Processo</t>
-  </si>
-  <si>
-    <t>Dt Emissão</t>
-  </si>
-  <si>
-    <t>Valor Realizado</t>
-  </si>
-  <si>
-    <t>Consultor Interno</t>
-  </si>
-  <si>
-    <t>Representante-pedido</t>
-  </si>
-  <si>
-    <t>Gerente Comercial-Pedido</t>
-  </si>
-  <si>
-    <t>Aplicação Mat./Serv.</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Nome Cliente</t>
-  </si>
-  <si>
-    <t>Cidade</t>
-  </si>
-  <si>
-    <t>UF</t>
-  </si>
-  <si>
-    <t>Tipo de Mercadoria</t>
-  </si>
-  <si>
-    <t>Subgrupo</t>
-  </si>
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Negócio</t>
-  </si>
-  <si>
-    <t>HON-MCXL-BASE</t>
-  </si>
-  <si>
-    <t>Base Teste FC</t>
-  </si>
-  <si>
-    <t>PVEN</t>
-  </si>
-  <si>
-    <t>999999</t>
-  </si>
-  <si>
-    <t>999998</t>
-  </si>
-  <si>
-    <t>FATURADO</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Andrey Andrade</t>
-  </si>
-  <si>
-    <t>André Camargo</t>
-  </si>
-  <si>
-    <t>005309</t>
-  </si>
-  <si>
-    <t>Produto</t>
-  </si>
-  <si>
-    <t>MicroClip</t>
-  </si>
-  <si>
-    <t>Detector Portátil</t>
-  </si>
-  <si>
-    <t>SSO</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -159,36 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -476,161 +424,269 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código Produto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Descrição Produto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Qtde Atendida</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Operação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status Processo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Dt Emissão</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Realizado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Consultor Interno</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Representante-pedido</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Gerente Comercial-Pedido</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Aplicação Mat./Serv.</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Nome Cliente</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Cidade</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Mercadoria</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Subgrupo</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Negócio</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HON-MCXL-BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Base Teste FC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PVEN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>999999</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>45915</v>
       </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" t="s">
-        <v>33</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Andrey Andrade</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>André Camargo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>005309</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HON-MCXL-BASE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Base Teste FC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PVEN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>999998</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>45915</v>
       </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" t="s">
-        <v>33</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Andrey Andrade</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>André Camargo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>005309</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Faturados.xlsx
+++ b/Faturados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
   <si>
     <t>Código Produto</t>
   </si>
@@ -79,9 +79,15 @@
     <t>HON-MCXL-BASE</t>
   </si>
   <si>
+    <t>HON-SENS-CS</t>
+  </si>
+  <si>
     <t>Base Teste FC</t>
   </si>
   <si>
+    <t>Teste Cross Selling</t>
+  </si>
+  <si>
     <t>PVEN</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>999998</t>
   </si>
   <si>
+    <t>CS-Test</t>
+  </si>
+  <si>
     <t>FATURADO</t>
   </si>
   <si>
@@ -100,16 +109,31 @@
     <t>Andrey Andrade</t>
   </si>
   <si>
+    <t>Rosilene</t>
+  </si>
+  <si>
     <t>André Camargo</t>
   </si>
   <si>
+    <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
     <t>005309</t>
   </si>
   <si>
+    <t>Cliente CS</t>
+  </si>
+  <si>
     <t>Produto</t>
   </si>
   <si>
+    <t>Reposição</t>
+  </si>
+  <si>
     <t>MicroClip</t>
+  </si>
+  <si>
+    <t>Sensor</t>
   </si>
   <si>
     <t>Detector Portátil</t>
@@ -477,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -547,43 +571,43 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2">
         <v>45915</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -591,43 +615,90 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2">
         <v>45915</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="J3" t="s">
+      <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="M3" t="s">
+      <c r="G4" s="2">
+        <v>45920</v>
+      </c>
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="I4" t="s">
         <v>31</v>
       </c>
-      <c r="S3" t="s">
+      <c r="J4" t="s">
         <v>32</v>
       </c>
-      <c r="T3" t="s">
+      <c r="K4" t="s">
         <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
